--- a/nr-prepare-release-2.1.0-ballot/ig/StructureDefinition-fr-core-observation-body-weight.xlsx
+++ b/nr-prepare-release-2.1.0-ballot/ig/StructureDefinition-fr-core-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:32:57+00:00</t>
+    <t>2024-07-17T12:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-prepare-release-2.1.0-ballot/ig/StructureDefinition-fr-core-observation-body-weight.xlsx
+++ b/nr-prepare-release-2.1.0-ballot/ig/StructureDefinition-fr-core-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:33:22+00:00</t>
+    <t>2024-07-17T14:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-prepare-release-2.1.0-ballot/ig/StructureDefinition-fr-core-observation-body-weight.xlsx
+++ b/nr-prepare-release-2.1.0-ballot/ig/StructureDefinition-fr-core-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:45+00:00</t>
+    <t>2024-07-17T15:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-prepare-release-2.1.0-ballot/ig/StructureDefinition-fr-core-observation-body-weight.xlsx
+++ b/nr-prepare-release-2.1.0-ballot/ig/StructureDefinition-fr-core-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:03:52+00:00</t>
+    <t>2024-07-17T15:28:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
